--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487495_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487495_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1617</v>
+        <v>2.9196</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6995</v>
+        <v>2.7686</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5377999999999999</v>
+        <v>0.1509</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.0887</v>
+        <v>-1.2283</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7349</v>
+        <v>0.3127</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3537</v>
+        <v>-1.541</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7718</v>
+        <v>1.8332</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1462</v>
+        <v>0.7179</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6254999999999999</v>
+        <v>1.1153</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.8604</v>
+        <v>-3.0615</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8812</v>
+        <v>-0.4052</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9792</v>
+        <v>-2.6563</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3502</v>
+        <v>2.1543</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3502</v>
+        <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0165</v>
+        <v>0.7769</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1604</v>
+        <v>-0.2811</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8561</v>
+        <v>1.0581</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7673</v>
+        <v>1.2166</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4658</v>
+        <v>2.7232</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4218</v>
+        <v>2.9402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.044</v>
+        <v>-0.217</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2283</v>
+        <v>-2.0887</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3127</v>
+        <v>-0.7349</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.541</v>
+        <v>-1.3537</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8332</v>
+        <v>0.7718</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7179</v>
+        <v>0.1462</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1153</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0615</v>
+        <v>-2.8604</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4052</v>
+        <v>-0.8812</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.6563</v>
+        <v>-1.9792</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6768</v>
+        <v>1.578</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.628</v>
+        <v>0.4011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9510999999999999</v>
+        <v>1.1769</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2166</v>
+        <v>1.7673</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9893</v>
+        <v>0.6928</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7015</v>
+        <v>0.3515</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2878</v>
+        <v>0.3412</v>
       </c>
       <c r="G4" t="n">
         <v>0.1943</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4032</v>
+        <v>0.1067</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4446</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0414</v>
+        <v>0.0121</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6404</v>
+        <v>0.6334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2121</v>
+        <v>-0.0355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4283</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8197</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6756</v>
+        <v>0.6686</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4317</v>
+        <v>0.1841</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2439</v>
+        <v>0.4845</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3905</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4241</v>
+        <v>-0.2825</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9609</v>
+        <v>0.3995</v>
       </c>
       <c r="G6" t="n">
         <v>-4.6573</v>
@@ -922,13 +922,13 @@
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>2.647</v>
+        <v>1.9404</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2999</v>
+        <v>0.1547</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3471</v>
+        <v>1.7857</v>
       </c>
       <c r="V6" t="n">
         <v>2.0427</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1285</v>
+        <v>-0.9225</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8179</v>
+        <v>-2.4515</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6894</v>
+        <v>1.529</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6951</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0954</v>
+        <v>0.3014</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4752</v>
+        <v>-0.1088</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5706</v>
+        <v>0.4102</v>
       </c>
       <c r="V7" t="n">
         <v>0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2698</v>
+        <v>-2.3454</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8094</v>
+        <v>-1.9118</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4604</v>
+        <v>-0.4337</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1454</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>0.326</v>
+        <v>0.2504</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0882</v>
+        <v>-0.0141</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2378</v>
+        <v>0.2645</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2754</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3349</v>
+        <v>-4.1556</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8031</v>
+        <v>-2.4367</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5318</v>
+        <v>-1.7189</v>
       </c>
       <c r="G9" t="n">
         <v>-5.7959</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4034</v>
+        <v>0.5827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7258</v>
+        <v>-0.3594</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1292</v>
+        <v>0.9421</v>
       </c>
       <c r="V9" t="n">
         <v>0.6659</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0723</v>
+        <v>-4.7931</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5032</v>
+        <v>-4.3844</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.4087</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0338</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0203</v>
+        <v>1.2995</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3305</v>
+        <v>0.4493</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6898</v>
+        <v>0.8502</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1003</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.124200000000001</v>
+        <v>-5.5301</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4355</v>
+        <v>-5.8416</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3113</v>
+        <v>0.3111999999999998</v>
       </c>
       <c r="G11" t="n">
         <v>-19.2699</v>
@@ -1312,13 +1312,13 @@
         <v>13.7094</v>
       </c>
       <c r="S11" t="n">
-        <v>6.9106</v>
+        <v>7.5046</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07369999999999977</v>
+        <v>0.5205</v>
       </c>
       <c r="U11" t="n">
-        <v>6.9842</v>
+        <v>6.9843</v>
       </c>
       <c r="V11" t="n">
         <v>2.318099999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2136</v>
+        <v>6.2902</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3236</v>
+        <v>2.5283</v>
       </c>
       <c r="F12" t="n">
-        <v>3.89</v>
+        <v>3.762</v>
       </c>
       <c r="G12" t="n">
         <v>5.1752</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4614</v>
+        <v>-0.3848</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9151</v>
+        <v>-0.7105</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4538</v>
+        <v>0.3257</v>
       </c>
       <c r="V12" t="n">
         <v>1.8915</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3421</v>
+        <v>4.4905</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4094</v>
+        <v>3.2047</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9327</v>
+        <v>1.2858</v>
       </c>
       <c r="G13" t="n">
         <v>5.4928</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1216</v>
+        <v>-0.9732</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9457</v>
+        <v>-1.1504</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1759</v>
+        <v>0.1772</v>
       </c>
       <c r="V13" t="n">
         <v>0.9502</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9971</v>
+        <v>1.0052</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8142</v>
+        <v>-0.2707</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8171</v>
+        <v>1.2759</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7117</v>
+        <v>0.7054</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5393</v>
+        <v>0.0892</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1724</v>
+        <v>0.6162</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7055</v>
+        <v>-0.0508</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6039</v>
+        <v>0.0204</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1016</v>
+        <v>-0.0712</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9938</v>
+        <v>0.7562</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0646</v>
+        <v>0.0687</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9292</v>
+        <v>0.6874</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.285</v>
+        <v>-0.0919</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1494</v>
+        <v>-0.22</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1356</v>
+        <v>0.1281</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9785</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2707</v>
+        <v>1.5072</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2492</v>
+        <v>-0.547</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7054</v>
+        <v>1.7117</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0892</v>
+        <v>0.5393</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6162</v>
+        <v>1.1724</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0508</v>
+        <v>2.7055</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0204</v>
+        <v>0.6039</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0712</v>
+        <v>2.1016</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7562</v>
+        <v>-0.9938</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0687</v>
+        <v>-0.0646</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6874</v>
+        <v>-0.9292</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3917</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1186</v>
+        <v>-0.3219</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.22</v>
+        <v>-0.4564</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1013</v>
+        <v>0.1345</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9412</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8016</v>
+        <v>0.8505</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9778</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7794</v>
+        <v>1.7259</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2798</v>
@@ -1702,13 +1702,13 @@
         <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3679</v>
+        <v>-0.3191</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0115</v>
+        <v>-0.065</v>
       </c>
       <c r="V16" t="n">
         <v>0.6659</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4313</v>
+        <v>0.8037</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4288</v>
+        <v>1.5311</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.7274</v>
       </c>
       <c r="G17" t="n">
         <v>4.7419</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8484</v>
+        <v>-0.4759</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3982</v>
+        <v>-0.2958</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4502</v>
+        <v>-0.1801</v>
       </c>
       <c r="V17" t="n">
         <v>-2.0913</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1395</v>
+        <v>0.0049</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5667</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7062</v>
+        <v>-0.0579</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3112</v>
+        <v>-0.4668</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5838</v>
+        <v>0.3523</v>
       </c>
       <c r="I18" t="n">
-        <v>4.895</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8144</v>
+        <v>0.652</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1807</v>
+        <v>0.1429</v>
       </c>
       <c r="L18" t="n">
-        <v>4.9952</v>
+        <v>0.5091</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5032</v>
+        <v>-1.1188</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4031</v>
+        <v>0.2094</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1001</v>
+        <v>-1.3281</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0911</v>
+        <v>-0.783</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2892</v>
+        <v>-0.8646</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3803</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3666</v>
+        <v>0.2754</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3335</v>
+        <v>-0.5707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1419</v>
+        <v>0.7714</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1916</v>
+        <v>-1.3421</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4668</v>
+        <v>3.3112</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3523</v>
+        <v>-1.5838</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8191000000000001</v>
+        <v>4.895</v>
       </c>
       <c r="J19" t="n">
-        <v>0.652</v>
+        <v>3.8144</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1429</v>
+        <v>-1.1807</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5091</v>
+        <v>4.9952</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1188</v>
+        <v>-0.5032</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2094</v>
+        <v>-0.4031</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3281</v>
+        <v>-0.1001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1213</v>
+        <v>-0.3402</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0692</v>
+        <v>-1.0845</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.052</v>
+        <v>0.7443</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2754</v>
+        <v>-2.3666</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.3666</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4685</v>
+        <v>-0.8259</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5117</v>
+        <v>-2.4094</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0432</v>
+        <v>1.5834</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1208</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2345</v>
+        <v>-0.592</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6775</v>
+        <v>-0.5752</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.0168</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0924</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7271</v>
+        <v>-2.6553</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2844</v>
+        <v>-1.6938</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4426</v>
+        <v>-0.9615</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2308</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8673</v>
+        <v>-0.7955</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5058</v>
+        <v>-0.9151</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3615</v>
+        <v>0.1197</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9714</v>
+        <v>-2.8645</v>
       </c>
       <c r="E22" t="n">
         <v>-4.6675</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6961</v>
+        <v>1.803</v>
       </c>
       <c r="G22" t="n">
         <v>0.2298</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5757</v>
+        <v>-0.4687</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4576</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1181</v>
+        <v>-0.0112</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2754</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.124199999999999</v>
+        <v>7.488799999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3112999999999992</v>
+        <v>-0.311399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>6.435599999999999</v>
+        <v>7.8001</v>
       </c>
       <c r="G23" t="n">
         <v>19.2698</v>
@@ -2248,13 +2248,13 @@
         <v>9.792200000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.910600000000001</v>
+        <v>-5.546199999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-6.9841</v>
+        <v>-6.9842</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07360000000000004</v>
+        <v>1.438</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3181</v>
